--- a/交付成果/第五轮精简版/待裁定清单（第5版核查）/待裁定清单_读书会01-25_第5版核查_含拟定稿.xlsx
+++ b/交付成果/第五轮精简版/待裁定清单（第5版核查）/待裁定清单_读书会01-25_第5版核查_含拟定稿.xlsx
@@ -11,11 +11,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="仍待裁定" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="已消失或已修订" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="仍待裁定·拟定稿" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="译名统一核查" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'全部条目·第5轮核查'!$A$1:$L$140</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'仍待裁定'!$A$1:$L$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'已消失或已修订'!$A$1:$L$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'译名统一核查'!$A$1:$F$71</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -15608,17 +15610,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="52" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15662,6 +15665,11 @@
           <t>依据／备注</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>知识库核对</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -15702,6 +15710,11 @@
           <t>旧说明：源课件作『要求』，转写脱字；属校勘而非义改。</t>
         </is>
       </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>源课件（《清净道论》性行段）原样；「要求」二字待比对课件原文。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -15742,6 +15755,11 @@
           <t>与第〔5〕〔6〕〔8〕〔9〕条句式对照，〔7〕条音义待回听原录音。</t>
         </is>
       </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>本库无对应课件；仍须回听原录音（[00:23:32]前后五盖对治段）。</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -15782,6 +15800,11 @@
           <t>『睡猴的瞌睡状态』疑为转写讹误，语义不通；对照上下文『怠惰状态(ālasiyabhāva)』的句式调整。</t>
         </is>
       </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>《清净之道》「昏沉睡眠」段可核；『睡猴』疑为『睡熟/沉滞』之讹，待比对课件原文。</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -15822,6 +15845,11 @@
           <t>旧裁定亦取『激发起来』；『提拔』与『精进』搭配不当。</t>
         </is>
       </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>属用词搭配问题，本库无对应条目。</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -15862,6 +15890,11 @@
           <t>旧建议即『保留原文＋存疑注』，第5版两条已各自带注，可维持。</t>
         </is>
       </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>五自在通说（转向·入定·决意·出定·省察）见《清净之道》；本库《清净之道》讲要可核。</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -15902,6 +15935,11 @@
           <t>āna＝入息、apāna＝出息、sati＝念；转写漏 a- 前缀、误拆 ssati。</t>
         </is>
       </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>已核：《大念处经》身随观入出息段（ānāpāna＝入出息，assasati/passasati），sati＝念。据《念诵集》《〈大念处经〉析解》。</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -15942,6 +15980,11 @@
           <t>同讲后文自用『乐想』；此为三颠倒中『乐颠倒』，作『乐想』方与常/我/净并列。</t>
         </is>
       </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>「乐想」为三颠倒（常·乐·我·净）之正名；本库三颠倒讲记可核。</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -15982,6 +16025,11 @@
           <t>原句『睁眼四圣谛』语义不全；义为所见当下即四圣谛。</t>
         </is>
       </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>属语义补足，本库无直接条目。</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -16022,6 +16070,11 @@
           <t>『未见』疑为『未来』；下文『慈悲没有敌人』即对未来的护佑。</t>
         </is>
       </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>本库未收录「未见／未来」条目；存疑。</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -16062,6 +16115,11 @@
           <t>本段对象为『第四个对象＝不喜欢／仇人』，原括注『（善人）』与前文『这位善人』相混，指代含混。</t>
         </is>
       </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>与讲者自述「第四个对象＝不喜欢的人」一致（同讲前段）。</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -16102,6 +16160,11 @@
           <t>脱『有』字。</t>
         </is>
       </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>脱字，本库无对应。</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -16142,6 +16205,11 @@
           <t>脱介词『从』。</t>
         </is>
       </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>脱介词，本库无对应。</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -16182,6 +16250,11 @@
           <t>『看别人肚子观了没观』不成句；义为比着别人坐多久、观得如何。</t>
         </is>
       </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>录音本处含糊，须回听。</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -16222,6 +16295,11 @@
           <t>按通行三十二身分，地界四组末位为『脑』，『尿』属水界两组的末位；原音频误将两组末位连读为『尿』。旧建议『尿→脑』即此。</t>
         </is>
       </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>已核：三十二身分地界四组末位为「脑」，水界第六组末位为「尿」。据《9三十二身分-古源尊者-20230712》录音原文。</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -16262,6 +16340,11 @@
           <t>《大念处经》为长部第22经，第21经为《帝释所问经》。</t>
         </is>
       </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>已核：《大念处经》＝长部第22经（《〈大念处经〉析解》引 D.2.373；中部对应 M.10）。</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -16302,6 +16385,11 @@
           <t>八圣道八支须各出现一次；原稿漏『正精进』且『正定』重复。第5版已有编者注，可据注直接改正正文或保留注。</t>
         </is>
       </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>八支圣道八支须各具；本库《道相应》讲记可核。</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -16342,6 +16430,11 @@
           <t>《金刚经》即作『歌利王』（忍辱仙人本生）；『嘎达布』为音译残字。</t>
         </is>
       </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>已核：汉译「歌利王」，音译「嘎拉布／嘎达布」，本生作《忍辱仙人本生经》。据《巴利三藏中的菩萨道思想10-忍辱巴拉密》。</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -16382,6 +16475,11 @@
           <t>该行为课件图示 OCR 散字混入正文，与下文重复。</t>
         </is>
       </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>图示散字混排，属 OCR/PDF 噪声。</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -16422,6 +16520,11 @@
           <t>『生爱』疑为『声爱』；此处对应六爱身序列，待回听。</t>
         </is>
       </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>本库未确证「六爱身」此处列表；存疑待回听。</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -16449,17 +16552,22 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>『各位尊者，各位〔法师〕，各位贤友，百善吉祥。』</t>
+          <t>保留原文，加注：〔『律师』疑为『尊者』之音误（参本库《上座部佛教名称勘误表》5.9『法师→尊者』），待回听〕。</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>改（用词订正）</t>
+          <t>保留原文＋加注</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>『律师』为『法师』之音近误；同一礼敬语他处多作『法师』。</t>
+          <t>勘误表 5.9：法师→尊者；本句尚须回听确认。</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>勘误表 5.9「法师→尊者」；本句「律师」尚须回听，暂存疑。</t>
         </is>
       </c>
     </row>
@@ -16502,6 +16610,11 @@
           <t>『围座星/美星/树形星/有阴性/双午十/越具/与所缘性/无阴星』为同段批量 ASR 讹字。</t>
         </is>
       </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>同段批量 ASR 讹字；本库《阿毗达摩》心法分类（89心）可作逐字校勘。</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -16542,6 +16655,11 @@
           <t>下文『你从，就事论事，还是一定要坚持你的观点，就是这个差别』可证。</t>
         </is>
       </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>本库无对应；存疑。</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -16582,6 +16700,11 @@
           <t>原为录音开头礼敬语，音译崩坏；依通行礼敬偈还原。</t>
         </is>
       </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>已核：《念诵集》礼敬偈作「Namo tassa bhagavato arahato sammāsambuddhassa」，勘误表 ASR 列亦同。</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -16622,6 +16745,11 @@
           <t>『布什八百米』为『布施巴拉密（dāna-pāramī）』之讹；本段正讲十巴拉密。</t>
         </is>
       </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>勘误表 5.5：「波罗蜜多→巴拉密」；「布施巴拉密（dāna-pāramī）」写法合规。据《巴利三藏中的菩萨道思想》课件。</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -16662,6 +16790,11 @@
           <t>旧建议即『与念诵集一致，加注即可』。</t>
         </is>
       </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>已核：《〈大念处经〉析解》经文列 31 项、无「脑」（与《身至念经》32 身分之差在「脑」）。</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -16702,6 +16835,11 @@
           <t>下文『客观世界的主要成因是火界』同一语脉；『时节的定律』多与四大（尤火界）并提。</t>
         </is>
       </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>本库 06_四界差别课件可核；「时节的定律」属四大（火界）语脉，存疑。</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -16742,6 +16880,11 @@
           <t>同段时间码[01:04:25]同句已作『支柱』，后一处误作『蜘蛛』。</t>
         </is>
       </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>同段前文已作「支柱」，属用词统一。</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -16782,6 +16925,11 @@
           <t>『解道行行者』为『解脱道行者』之讹。</t>
         </is>
       </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>勘误表未收录「解脱道行者」；依字义订正，存疑。</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -16822,6 +16970,11 @@
           <t>源 txt 巴利语脱符，以?替代；据《清净道论》/帕奥体系通行写法补正。</t>
         </is>
       </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>本库巴利正字以《念诵集》／阿毗达摩论典为准；源 txt 脱符需补。</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -16849,17 +17002,22 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>『古源尊者讲述』</t>
+          <t>按本库《上座部佛教名称勘误表》2.6，规范作『古源尊者讲述』；如坚持照录课件，则保留『古源如应讲述』并加注〔即古源尊者（Uttama）〕。二者择一，全书统一。</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>改（订正）</t>
+          <t>改（译名规范）或保留＋加注</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>『古源如应』当为『古源尊者（Uttama）』；参读书会23 同署『古源(Uttama)尊者讲述』。</t>
+          <t>勘误表 2.6「古源→古源尊者」；本库《15_天随念》《30_僧随念3》课件署『古源如应讲述』。</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>已核：勘误表 2.6 规定「古源／古源法师／古源禅师→古源尊者」；而本库课件（《15_天随念》《30_僧随念3》）署名作「古源如应讲述」，属课件原有署名。</t>
         </is>
       </c>
     </row>
@@ -16902,6 +17060,11 @@
           <t>第5版已在材料说明中列出该组音近字对照，可维持照录＋注。</t>
         </is>
       </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>已核：八事＝佛·法·僧·戒·定·慧·过去未来五蕴·缘起；据《第72课 信心所3》共修版。</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -16929,17 +17092,22 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>『回答者是〔阿拉汉〕比库尼法施。』</t>
+          <t>『回答者是阿拉汉比库尼法施。』（勘误表规范＝阿拉汉）加注：〔源件作『阿拉罕』〕。</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>改（订正）</t>
+          <t>改（译名规范）＋加注</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>『阿拉罕』为『阿拉汉』之讹。</t>
+          <t>勘误表 5.5 规范＝阿拉汉；《小问答经讲记》源件正文作『阿拉罕』、礼敬语作『阿拉汉』。</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>已核：勘误表 5.5 规范为「阿拉汉」，「阿拉罕」列为存疑；《小问答经讲记》源件正文作「阿拉罕」、礼敬语作「阿拉汉」。</t>
         </is>
       </c>
     </row>
@@ -16969,17 +17137,22 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>『2025年11月〔　〕日』</t>
+          <t>保留原文并加注：〔源件作『2025年11日』，脱『月』字，待补〕；或径改为『2025年11月〔　〕日』。</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>改（补脱字）</t>
+          <t>保留＋加注 或 改（补字）</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>源文脱『月』字，日期待补。</t>
+          <t>《小问答经讲记》课件原文即作『2025年11日』。</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>已核：《小问答经讲记》课件原文即作「2025年11日」（源件脱「月」），且课件内「小问答经／小问答答经」标题混见。</t>
         </is>
       </c>
     </row>
@@ -17009,17 +17182,22 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>『答：〔毗舍佉〕贤友！那执取既非……』（并与正文他处统一为『毗舍佉』）</t>
+          <t>全书统一为『维沙卡（Visākhā）』：『答：维沙卡贤友！那执取既非……』</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>改（统一译名）</t>
+          <t>改（译名统一）</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>正文他处已作『毗舍佉』；『毗舍伝／毗舍伎』为同音异写。旧建议作『维沙卡(Visākhā)』，与本书现行译名『毗舍佉』不同，宜就地统一。</t>
+          <t>勘误表 2.4「毘舍佉→维沙卡（Visākhā）」；源件作『毗舍佉／毗舍伝』。全书该名共 94 处需一并评估。</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>已核：勘误表 2.4「毘舍佉 → 维沙卡（Visākhā）」；《小问答经讲记》源件作「毗舍佉」，正文另处作「毗舍伝」。</t>
         </is>
       </c>
     </row>
@@ -17062,6 +17240,11 @@
           <t>『出世问道』为『出世间的道』之讹。</t>
         </is>
       </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>属用词，本库未收录。</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -17102,6 +17285,11 @@
           <t>旧说明即『源文占位符，保留』。</t>
         </is>
       </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>已核：源件占位符，勘误表规定无法确证者标「存疑（待核实）」，不得臆改。</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -17142,6 +17330,11 @@
           <t>『军工』疑为『统统／通通』之音误；录音本处含糊，可标〔待核〕。</t>
         </is>
       </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>录音本处含糊，须回听。</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -17182,6 +17375,11 @@
           <t>『不想受』语义不完，义为『不（负责）感受』。</t>
         </is>
       </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>录音语义补足，须回听。</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -17222,6 +17420,11 @@
           <t>第5版4周版已有同注，8周版可补同注。</t>
         </is>
       </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>已核：三十二身分第三组为心·肝·膜（肋膜）·脾·肺；源课件「脾脏的自分界限」疑误置，应作「肺脏」。</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -17262,6 +17465,11 @@
           <t>本篇为《天随念》课件，正文『施随念』与题不符，然属课件原误，照录＋注为宜。</t>
         </is>
       </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>已核：源课件第三条第3点原文确作「唯以其心贴切于『施随念』业处禅法」。据《15_天随念-古源尊者-20250119（课件）》（题为《天随念》）。</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -17302,6 +17510,11 @@
           <t>『用品塔』义为『值得礼敬/应受礼敬之处』，原文『都是用品塔』语意未完。</t>
         </is>
       </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>已核：源课件原文确作「甚至比库的物品，如袈裟、钵、腰带都是用品塔」，对应巴利 Añjalikaraṇīyo「应礼敬」。据《30_僧随念3-古源尊者-20250203（课件）》。</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -17342,8 +17555,2004 @@
           <t>三皈依巴利语为『Buddhaṃ saraṇaṃ gacchāmi』，原文衍一『Saraṇaṃ』。</t>
         </is>
       </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>已核：三皈依规范为单次 saraṇaṃ「Buddhaṃ saraṇaṃ gacchāmi」（佛行双 Saraṇaṃ 属衍文）。据《上座部佛教念诵集》《三皈依2（课件）》。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F71"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>误写／旧译</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>规范写法</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>命中次数</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>涉及文件数</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>示例1（书次·行·片段）</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>示例2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>八正道</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>八支圣道</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>411</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>读书会05_日常生活 L106: &gt; [00:21:24.080] 再一个就是无痴正知。从狭义上讲，它就是要见到名色法……但是我们现在做不到，所以从广义的角度上，就是我以前经</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>读书会05_日常生活 L344: &gt; 建议面对果报时以正念观察感受，运用慈悲聆听、认知共情替代预设标签与强制要求，并以有益正知等守护心，通过四念处与八正道转化认知模式。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>善知识</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>善友</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>182</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>读书会01_禅修入门 L416: &gt; 第五个是结交善知识——对那种比较精进的人，你会受到他的影响；而且呢，他对于怎么去处理这种昏沉睡眠，有很多的建议和方法。</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>读书会01_禅修入门 L424: &gt; 〔00:34:28〕论书里面讲，有六种方法可以帮助灭除掉举和追悔：第一个，对于佛法有深入的认识；第二个是发问；第三个是了解戒律；第四个是</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>清净道论</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>《清净之道》</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>177</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>读书会01_禅修入门 L309: &gt; 《清净道论》提及六种性行,即贪行者、瞋行者、痴行者、信行者、觉行者、寻行者,一些注疏中甚至提到六十三种性行。在此,我们只讨论《清净道论》</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>读书会01_禅修入门 L350: &gt; (2) 依据完整的巴利三藏及《清净道论》;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>萨迦耶见</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>有身见</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>读书会05_日常生活 L367: - **不要被术语吓住**：sati、sampajañña、四念处、业处、萨迦耶见、名色法……主持人只需照读，不必解释；有人问就说："我们跟</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>读书会05_日常生活 L425: - **术语分寸**：saññā、三颠倒、萨迦耶见、啸叫效应——照读不解释；有人问就答："读几周自然就熟了。"</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>毗舍佉</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>维沙卡</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>读书会23_小问答经 L76: **📖 本周共读导读（主持人了解即可，不用念）**：今晚六段材料是「同一件事的六个侧面」。**材料①（讲01课件）是经题与第一问答**——「</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>读书会23_小问答经 L78: **朗读分工建议**：材料①、②由一人读（篇幅短、密度高）；材料③只读「有身见」一问答、「有身集」一问答与经尾第467节（中间跳读处按文内〔</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>阿罗汉</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>阿拉汉</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>读书会01_禅修入门 L274: &gt; (6) 具足悟阿罗汉果的条件</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>读书会04_持戒与戒 L148: &gt; “何为有限清净戒？未受具足戒者所受有限学处，是名有限清净戒。何为无限清净戒？已受具足戒者所受无限学处，是名无限清净戒。何为圆满清净戒？凡</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>不净观</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>不净修习</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>读书会03_四护卫禅 L27: &gt; 本周主题：四护卫禅总论。佛陀给走上修行之路的人准备了四件“护身之物”——慈心禅、佛随念、不净随念、死随念，合称“四护卫禅”，又称为“一切</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>读书会03_四护卫禅 L95: **四、第三种护卫禅——不净观：去除对自己、对他人的贪爱**</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>安般</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>入出息</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>读书会01_禅修入门 L433: 2. **下周预告**：下周开始进入方法——"呼吸怎么找、整条路怎么走"：入出息念基础方法——取相点与安般十六步框架。</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>读书会01_禅修入门 L471: &gt; 📚 **下一份文档**：`第2周_安般念修法与数息对治_主持人版.md`</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>阿僧祇</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>无数</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>读书会01_禅修入门 L284: &gt; 1. 智慧型:四阿僧祇十万大劫</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>读书会01_禅修入门 L285: &gt; 2. 信心型:八阿僧祇十万大劫</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>帕奥禅师</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>帕奥西亚多</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>读书会02_慈心禅修 L136: - **文件**：智慧之光（修订版）· 第六章 四护卫业处（缅甸帕奥禅师著）</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>读书会02_慈心禅修 L408: - 《智慧之光·第六章 四护卫业处（帕奥禅师著）》——四护卫禅总说，慈心修习居首。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>比丘</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>比库</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>读书会14_阿毗达摩 L96: [00:20:17.600] 那举个例子，比如说佛陀证悟以后讲的第一部经转法轮经，那就是那个时候的当机众，只有五个比库，就是五比丘。以衮丹雅</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>读书会14_阿毗达摩 L486: &gt; 提示：回到材料②"四、思"：思是"引领心和其他心所与它一起生起"的组织力，像公司里的秘书、像战场上的指挥官，驱使心与心所"都好像是贯穿了</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>南无</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>那摩</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>读书会11_十二缘起 L242: [00:00:00.000] 大家请合照，我们一起来一进破土。南无阿萨，南无多萨，南无阿三。礼敬那位世尊，阿罗汉正自觉者，各位尊者，各位名师</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>读书会16_突破生命 L71: [00:00:00.000] 大家请科长。忙起来，李静好多。南无拉萨玛卡瓦多阿拉玛多萨玛三摩嘎萨，南无萨多阿拉哈多萨三摩嘎萨，南无拉萨嘎瓦多</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>法师</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>尊者</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>读书会03_四护卫禅 L197: &gt; [00:00:07] 好，大家请合掌，我们一起来礼敬佛陀（巴利礼敬颂，转写从略）。各位尊者、各位法师、各位贤友，晚上吉祥。好，今天是卫塞</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>读书会11_十二缘起 L398: 8. **不越界、不承诺**：主持人不是心理医生，也不是法师。若有人谈及严重的心理困扰，只倾听、不诊断、不给「法药式」的保证，可温和建议其寻</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>须陀洹</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>入流</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>读书会09_四圣谛（ L95: 因为有四道、四果：须陀洹道、斯陀含道、阿那含道和阿拉汉道，对应有四个果，所以总共就是八种出世间心（后面会讲为什么会有 40 种出世间心）。道</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>读书会14_阿毗达摩 L300: - 四道心：须陀洹（入流）道心、斯陀含（一来）道心、阿那含（不来）道心、阿罗汉道心</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>辟支</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>独觉</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>读书会10_八正道实 L108: 这里的「一时」是指佛陀成道之后两个月，在阳历七月的月圆日（雨季安居前一天）。那时佛陀从菩提伽耶（Bodhgaya）来到仙人坠处（Isipat</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>读书会16_突破生命 L261: [00:05:18.280] 第一个，你说我的生命意识为了证悟涅槃佛教徒，这个普遍的要么就是解脱，要么就成佛。解脱两种，一个阿拉汉的解脱，一</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>薄伽梵</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>跋格瓦</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>读书会23_小问答经 L109: 问：毗舍佉近事男对法施比库尼这么 说：，尊姊！所谓'萨迦耶，萨迦耶'，尊姊！什么被薄伽梵说为萨迦耶呢？'</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>读书会23_小问答经 L111: 答：毗舍佉贤友！这些五取蕴被薄伽梵说是萨迦耶，即：色取蕴、受取蕴、想取蕴、行取蕴、识取蕴，这些五取蕴被薄伽梵说为萨迦耶。'</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>鹿野苑</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>仙人堕处</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>读书会03_四护卫禅 L241: &gt; [00:39:06] 那么弘法？首先他就想到说：那谁可以作为他首先度化的对象？他想起来是那前面（的）两位（老师），对？然后结果，他想到第</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>读书会08_四圣谛（ L27: &gt; 本周主题：四圣谛总说——如实了知苦集灭道。一句话：佛陀在鹿野苑第一次"转法轮"，说出的正是四圣谛——苦、苦之集、苦之灭、导至苦灭之道；帕</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>舍利弗</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沙利子</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>读书会08_四圣谛（ L231: &gt; 那拘罗父居士听闻世尊的教导后，欢喜信受，从座而起，向世尊顶礼，右绕而去，前往尊者舍利弗所在之处；到了之后，向尊者舍利弗顶礼，坐在一旁。坐</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>读书会08_四圣谛（ L243: &gt; "尊者，我们即使远道而来，也愿在舍利弗尊者座下听闻此法义。恳请尊者为我们开示其中深意。"</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>毗钵舍那</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>维巴沙那</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>读书会20_从凡夫到 L268: &gt; 观，巴利语vipassanā，又音译为维巴沙那。为直观觉照一切名色法（身心现象）的无常、苦、无我本质，亦即培育智慧的修行法门。古音译作毗</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>读书会23_小问答经 L36: | 核心问题 | **佛陀为什么把「萨迦耶」直接等同于「五取蕴」？「取蕴」与「蕴」差在哪里、这个「取」是「谁」在取？让五蕴不断再生的「萨迦耶</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>阿修罗</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>阿苏罗</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>读书会02_慈心禅修 L73: 五、为非人所爱（鬼界、阿修罗、夜叉也喜欢你，不会害你、不会给你捣乱。）</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>读书会09_四圣谛（ L83: 第二个世间叫有情世间。有情世间就是我们这 31 界生命，简称为三界：欲界、色界、无色界。有地狱、恶鬼、畜生、阿修罗、人，六层欲界天、色界天和</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>辟支佛</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>独觉</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>读书会10_八正道实 L108: 这里的「一时」是指佛陀成道之后两个月，在阳历七月的月圆日（雨季安居前一天）。那时佛陀从菩提伽耶（Bodhgaya）来到仙人坠处（Isipat</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>读书会16_突破生命 L261: [00:05:18.280] 第一个，你说我的生命意识为了证悟涅槃佛教徒，这个普遍的要么就是解脱，要么就成佛。解脱两种，一个阿拉汉的解脱，一</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>难陀</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>难德</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>读书会02_慈心禅修 L102: 关于慈心禅的第七项利益"不被火、毒药与武器所伤害"。举几个佛陀时代的例子来说明。佛陀时代有两位杰出的在家女弟子，其中一位是优陀罗（Uttar</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>读书会05_日常生活 L60: ### 原文材料①：行处正知——四种比库；守护根门（难陀尊者）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>兜率</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>喜足</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>读书会03_四护卫禅 L205: **二、入胎：从兜率天以正念正知入母胎**</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>读书会03_四护卫禅 L207: &gt; [00:05:42] 2640多年前，有一位（住在）兜率天的天子，他观察自己，到人间来成佛的这个因缘到了。他需要找一位寿元呢只剩下十个月</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>阿那含</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>不来</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>读书会07_四念处（ L318: - **"对治"不是"压抑"（本周最容易被误听的一句）**：有组员会把灭嗔六法听成"我不该生气、生气就是失败"。回应时把原文的刻度摆出来：材</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>读书会09_四圣谛（ L95: 因为有四道、四果：须陀洹道、斯陀含道、阿那含道和阿拉汉道，对应有四个果，所以总共就是八种出世间心（后面会讲为什么会有 40 种出世间心）。道</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>波罗奈</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>巴拉纳西</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>读书会09_四圣谛（ L27: &gt; 本周主题：涅槃与道果的证悟原理。前六周我们把"灭什么（灭谛）"和"怎么走（道谛）"讲清楚了，本周回答最后一步的落地问题：**道智与果智如</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>读书会09_四圣谛（ L208: **一、世尊波罗奈仙人住处鹿野苑开头背景段（舍二边、得中道）**</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>僧残</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>桑喀地谢思</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>读书会04_持戒与戒 L154: - **文件**：《小戒学-根本戒学 Khuddasikkhā-Mūlasikkhā》（“忏悔法释”“僧残罪释论”“布萨品”“自恣解说”“知</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>读书会04_持戒与戒 L432: - **不要被术语吓住**：杂染、四杂染、残缺/穿孔/斑驳/杂色、淫欲七小缚、发露、学处、波罗夷/僧残/波逸提、别住、摩那埵……主持人只需照</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>提婆达多</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>迭瓦达德</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>读书会16_突破生命 L274: [00:56:10.525] 听说有以前这个提婆达多，有一生，这个佛陀是个国王。听说有一个人专门猎取国王的脑袋？那时的菩萨？讲说太好了，终于</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>读书会17_菩萨道思 L282: &gt; ⚠️ **主持人操作**：共读原文只读不解释。建议分工朗读：材料①（音声转写）由一位法友读，材料②（论文）由另一位法友读，材料③（论文）</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>巴嘎瓦</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>跋格瓦</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>读书会22_四预流支 L202: &gt; [00:00:11.960] 大家请合掌。我们一起来礼敬佛陀。南无那萨巴嘎瓦多，阿拉多三藐三菩拉萨。南无大嘎瓦多，阿拉多萨三。南无拉萨，</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>读书会22_四预流支 L49: &gt; 南无达萨 巴嘎瓦多 阿拉哈多 三藐三菩陀。（Namo Tassa Bhagavato Arahato Sammāsambuddhassa</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>舍卫</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沙瓦提</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>读书会08_四圣谛（ L266: &gt; 舍卫城因缘。"比库们啊，色是无常的，无论是过去的还是未来的；更何况现在的色呢！如此观察的比库们啊，多闻的圣弟子对过去的色无有希求；不欣乐</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>读书会08_四圣谛（ L272: &gt; 十一、舍卫城因缘"诸比库！色非我，过去未来皆然；何况现在！如是观者，诸比库！多闻圣弟子于过去色无有希求；于未来色不生欣乐；于现在色修习厌</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>斯陀含</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>一来</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>读书会09_四圣谛（ L95: 因为有四道、四果：须陀洹道、斯陀含道、阿那含道和阿拉汉道，对应有四个果，所以总共就是八种出世间心（后面会讲为什么会有 40 种出世间心）。道</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>读书会14_阿毗达摩 L300: - 四道心：须陀洹（入流）道心、斯陀含（一来）道心、阿那含（不来）道心、阿罗汉道心</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>毗婆舍那</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>维巴沙那</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>读书会01_禅修入门 L85: &gt; [00:08:08] 过去用我们古汉语翻译成"毗婆舍那"。毗婆舍那，如果用客家话来念，也是"维巴萨那"。</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>读书会01_禅修入门 L87: &gt; [00:08:19] 维巴萨那也是组合词，就是"维"（vi）加"巴萨那"（passanā）。"维"（vi）在巴利里的意思是"不同""多样</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>三昧</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>三摩地</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>读书会03_四护卫禅 L234: &gt; [00:00:54] 当你慈心起来的时候……我们（很多人）念过《观音菩萨普门品》，对？念观音菩萨名号有那么多功德，然后为什么我们念了没用</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>读书会03_四护卫禅 L244: &gt; [00:03:33] 那为什么她会这样？（乌达拉）在（油泼来的）那个当下，立即进入慈心三昧，（心中）对这个人没有一丝丝的怨恨、生气，所以</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>夜摩</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>亚马</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>读书会09_四圣谛（ L248: 当世尊转动法轮时，大地诸天发出欢呼："世尊在波罗奈城仙人堕处的鹿野苑，已转动无上法轮，此轮非沙门、婆罗门、天人、魔罗、梵天或世间任何众生所能</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>读书会13_业与轮回 L78: [00:07:35.260] 来四大天王天，它的寿命就这个九百天年……再往上呢，就叫三十三天……兜率天……夜摩天……化乐天……最高的欲界天，</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>波罗夷</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>巴拉基格</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>读书会04_持戒与戒 L160: &gt; （《小戒》382）舍离比库身份之悔，名为波罗夷忏悔；如前所说出罪法，是重罪之忏悔仪。</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>读书会04_持戒与戒 L432: - **不要被术语吓住**：杂染、四杂染、残缺/穿孔/斑驳/杂色、淫欲七小缚、发露、学处、波罗夷/僧残/波逸提、别住、摩那埵……主持人只需照</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>波逸提</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>巴吉帝亚</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>读书会04_持戒与戒 L170: &gt; （《小戒》397）（忏）尊者，我犯一条波逸提罪。我犯二条乃至多条波逸提罪。（忏）尊者，我犯应呵责法、非善法、应对首忏悔法，今向您忏悔。此</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>读书会04_持戒与戒 L432: - **不要被术语吓住**：杂染、四杂染、残缺/穿孔/斑驳/杂色、淫欲七小缚、发露、学处、波罗夷/僧残/波逸提、别住、摩那埵……主持人只需照</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>僧伽</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>僧团</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>读书会20_从凡夫到 L303: &gt; 入流圣者已经断除了邪见，他们不可能在任何情况下故意造作诸如杀生、偷盗、邪淫、妄语之类的恶行，即使是在梦中，他们也不会再造作此类的恶业，因</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>读书会22_四预流支 L194: &gt; 巴利：Buddhaṃ saraṇaṃ gacchāmi, Dhammaṃ saraṇaṃ gacchāmi, Saṅghaṃ saraṇ</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>夜叉</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>亚卡</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>读书会02_慈心禅修 L73: 五、为非人所爱（鬼界、阿修罗、夜叉也喜欢你，不会害你、不会给你捣乱。）</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>读书会02_慈心禅修 L144: 修习佛随念亦可使自己不遭受厄难，保护不受夜叉、鬼神等的干扰，也可使心清晰，因此当心不清晰时亦应修佛随念。当悚惧感（saṃvega）退失及心攀</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>目犍连</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>马哈摩嘎蓝</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>读书会01_禅修入门 L420: &gt; 〔00:28:12〕那我们在很多的书里面呢，提到佛陀教导目犍连尊者对治昏沉睡眠的八种方法，有的时候（说）七种方法。</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>读书会17_菩萨道思 L122: [00:19:50.265] 我们讲佛陀有实力，那么证得这样的菩提的圣者称为独觉佛。那未来的这个佛陀上首弟子，就是他的上首弟子，就像我们佛陀</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>优波难陀</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>伍巴难德</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>读书会07_四念处（ L214: **（② 优波难陀的故事）**【◈扩展，时间富余时读】</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>读书会07_四念处（ L216: &gt; 帕奥西亚多在《正念之道》讲到一个优波难陀(Upananda)的故事。优波难陀到处去骗袈裟。因为他比较会讲法，到处去拿袈裟。而且他用各种计</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>耆婆</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>基瓦</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>读书会25_随念修习 L166: &gt; ⚠️ 主持人操作：本件为**正文主体**，转写为自动语音识别原始稿，讹字较多（「天水链／天水念」＝天随念；「进行定」＝近行定；「四名运」</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>读书会25_随念修习 L509: 5. **本周是「框架与取舍」，不要急着深入定学细节。** 材料②只取三段（必读「天界取舍」＋选读「欲界六天/耆婆/四种功德」），**「近行</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>罗睺罗</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>拉胡勒</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>读书会01_禅修入门 L92: &gt; 〔00:14:57〕佛陀呢，在中部《入出息念经》里面讲：诸比库，修习、多作入出息念，有大果报、有大利益。诸比库，修习、多作入出息念，能圆</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>读书会21_破妄显真 L275: &gt; ⚠️ 主持人操作：本讲全长 63 分钟，**全读必超时**。只读下列三段（①「疑以调查双方为借口」开头至「无药可治」；②「而所谓的双向调</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>白骨观</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>白骨想</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>读书会17_菩萨道思 L201: **（主持人操作）** 本周练习意在「体会发心」而非「盘点成绩」，全程语调温柔、不加评判。若时间紧（约8 min），只做「想起一件小事→感受</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>读书会17_菩萨道思 L215: &gt; ⚠️ 主持人操作：只照读下面两段——①「十巴拉密逐一省察」（[00:00:18.200]–[00:27:29.200]，必读）；②「布施</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>比丘尼</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>比库尼</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>读书会20_从凡夫到 L136: &gt; 答：想要修行直到证得初果，对在家人来说，至少应当守持五戒，若有条件还要受持八戒。对出家人来说，北传是比丘、比丘尼、式叉摩那、沙弥、沙弥尼</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>读书会23_小问答经 L78: **朗读分工建议**：材料①、②由一人读（篇幅短、密度高）；材料③只读「有身见」一问答、「有身集」一问答与经尾第467节（中间跳读处按文内〔</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>善哉</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>萨度</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>读书会04_持戒与戒 L164: &gt; （《小戒》384）“尊者，我犯了一条粗罪，今向您忏悔。”说完后，若对方问：“贤友，你可见此罪过？”应回答：“是的，尊者，我见此罪过。”若</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>读书会04_持戒与戒 L226: &gt; （《小戒》384）“尊者，我犯了一条粗罪，今向您忏悔。”说完后，若对方问：“贤友，你可见此罪过？”应回答：“是的，尊者，我见此罪过。”若</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>阿拉罕</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>阿拉汉(待核)</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>读书会23_小问答经 L125: 回答者是阿拉罕比库尼法施。</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>读书会23_小问答经 L139: 回答者是阿拉罕比库尼法施。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>沙弥</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沙马内勒</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>读书会02_慈心禅修 L104: 另一个是莎玛瓦蒂王后（Sāmāvatī）的故事，她有一位侍女叫姑如达拉（Khujjuttarā），是佛陀另一位突出的在家女弟子。此侍女经常去</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>读书会20_从凡夫到 L136: &gt; 答：想要修行直到证得初果，对在家人来说，至少应当守持五戒，若有条件还要受持八戒。对出家人来说，北传是比丘、比丘尼、式叉摩那、沙弥、沙弥尼</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>迦毗罗卫</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>咖毕勒瓦土</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>读书会03_四护卫禅 L207: &gt; [00:05:42] 2640多年前，有一位（住在）兜率天的天子，他观察自己，到人间来成佛的这个因缘到了。他需要找一位寿元呢只剩下十个月</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>读书会17_菩萨道思 L104: [00:11:00.540] 这个故事，这个过程，就是我们一开始的时候讲，就是佛陀在他的家乡迦毗罗卫城示现双神变。那么舍利弗尊者，这个感受到</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>慈心观</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>慈心修习</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>读书会03_四护卫禅 L198: &gt; 修习体系（四护卫禅各对治一种烦恼，附经典依据）：佛随念对治疑与怯弱（《增支部》VI.10）；慈心观对治嗔恨（《慈经》）；不净观对治贪欲（</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>读书会19_戒定慧三 L140: &gt; 在帕奥禅林的禅修者可以选择从安般念或四界分别观入门。对于后者，当透过修习四界分别观培育起定力，而且光很稳定之后，就可以转修三十二身分，进</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>帝须</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>帝思</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>读书会04_持戒与戒 L104: &gt; 不取随相是对于能使烦恼显现而得通名为随相的手、足、微笑，我们讲牙齿很漂亮、头发很美丽、笑容很可爱，一笑两酒窝，说话美丽动听像银铃般，经常</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>读书会04_持戒与戒 L106: &gt; 这里有个例子，就是塔山的大帝须长老，大家熟悉。长老从塔山来到阿努拉塔补勒去乞食。路上碰到一位跟丈夫吵架的女子，她装扮得像天女一样美丽，准</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>耶输陀罗</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>亚寿特拉</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>读书会10_八正道实 L152: 佛陀说两种极端当中的一种是沉迷于感官享乐。我们的菩萨──悉达多太子（Prince Siddhattha）──在出家之前享受了许多年的感官欲乐</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>读书会22_四预流支 L114: [00:10:22.250] 要成佛的，这个行者，他需要这个先被一尊活着的佛陀授记，他被授记的时候，他需要有这个具足这个八个条件，一般在。这</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>迦叶</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>咖沙巴</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>读书会12_缘起深入 L240: 第三种呢，这个我们叫巴拉密，这个就是善的习惯，良善的习惯，尤其呢，是导向于解脱的这种身心留下来这种习惯，我们称为叫巴拉密。好，所以这个我们当</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>读书会09_四圣谛（ L47: &gt; 今天还会读到一批很美的经文——觉支相应。佛陀说，七觉支就像尖顶阁上的椽木，根根朝向顶尖；修习它们，心就"倾向涅槃、朝向涅槃、指向涅槃"。</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>须菩提</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>苏菩帝</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>读书会02_慈心禅修 L106: 拥有慈心禅的人也能像须菩提（Subhūti）尊者一般容易获得定力。佛陀八十大弟子中须菩提是慈心禅第一的比库，他以慈心禅作为基础来修行观禅，最</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>读书会02_慈心禅修 L102: 拥有慈心禅的人也能像须菩提（Subhūti）尊者一般容易获得定力。佛陀八十大弟子中须菩提是慈心禅第一的比库，他以慈心禅作为基础来修行观禅，最</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>阿兰若</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>林野</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>读书会02_慈心禅修 L262: - sakko：堪能／有能力——住阿兰若的比库想要住于"证知寂静的境界"……即拥有第二、第四精勤支</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>读书会02_慈心禅修 L71: - **sakko（堪能／有能力）**——住阿兰若的比库想要住于"证知寂静的境界"……即拥有第二、第四精勤支。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>发菩提心</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>决定</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>读书会03_四护卫禅 L268: &gt; [00:09:04] 那真正的慈心（禅）修习，它是我们要达成的，要慈心遍满。我们经常讲说：你这个人要有菩提心、要有慈心，但是要什么样的慈</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>读书会03_四护卫禅 L110: &gt; [00:09:04] 那真正的慈心（禅）修习，它是我们要达成的，要慈心遍满。我们经常讲说：你这个人要有菩提心、要有慈心，但是要什么样的慈</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>车匿</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>阐那</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>读书会03_四护卫禅 L223: &gt; [00:30:05] 菩萨悉达多太子到29岁的时候，他的心智相当成熟了，他见到了五欲的危害和出离的功德利益。当时，他想要去游访这个王家花</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>读书会03_四护卫禅 L90: &gt; [00:30:05] 菩萨悉达多太子到29岁的时候，他的心智相当成熟了，他见到了五欲的危害和出离的功德利益。当时，他想要去游访这个王家花</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>频婆娑罗</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>宾比萨勒</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>读书会03_四护卫禅 L393: - **呵欲引文（《童蒙止观》）与"频婆娑罗王"典故**：照读即可，不展开戒律讨论；若有人问"这是不是要求佛教徒不能爱美"，回答："原文的对</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>读书会03_四护卫禅 L197: - **呵欲引文（《童蒙止观》）与"频婆娑罗王"典故**：照读即可，不展开戒律讨论；若有人问"这是不是要求佛教徒不能爱美"，回答："原文的对</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>羯磨</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>甘马</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>读书会04_持戒与戒 L473: - **术语别吓住自己**：学处、五戒、八戒、九分戒、活命八戒、邪命、三皈依、甘马（羯磨）、veramaṇī（离）……主持人只需照读，不必解</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>读书会04_持戒与戒 L234: - **术语别吓住自己**：学处、五戒、八戒、九分戒、活命八戒、邪命、三皈依、甘马（羯磨）、veramaṇī（离）……主持人只需照读，不必解</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>菩提伽耶</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>布特嘎亚</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>读书会10_八正道实 L108: 这里的「一时」是指佛陀成道之后两个月，在阳历七月的月圆日（雨季安居前一天）。那时佛陀从菩提伽耶（Bodhgaya）来到仙人坠处（Isipat</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>读书会10_八正道实 L172: 这里的「一时」是指佛陀成道之后两个月，在阳历七月的月圆日（雨季安居前一天）。那时佛陀从菩提伽耶（Bodhgaya）来到仙人坠处（Isipat</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>三法印</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>三相</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>读书会14_阿毗达摩 L426: 就像有毒的树会结有毒的果实，在众生的心相续流中也一样，有一种元素(dhātu)，会覆盖住应被了解的佛法(Dhamma)。这种元素称为随眠的痴</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>读书会14_阿毗达摩 L293: 就像有毒的树会结有毒的果实，在众生的心相续流中也一样，有一种元素(dhātu)，会覆盖住应被了解的佛法(Dhamma)。这种元素称为随眠的痴</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>黄门</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>般哒格</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>读书会17_菩萨道思 L266: [00:13:02.440] 第二个呢，他是男性啊，就是是已得人人身者啊，只有男人所发的至善愿才有效，而女性、黄门、无性人以及阴阳人所发的愿</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>读书会17_菩萨道思 L198: &gt; **[00:13:02.440]** 第二个呢，他是男性啊，就是是已得人人身者啊，只有男人所发的至善愿才有效，而女性黄门和无姓人以及阴阳</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>阎浮提</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>瞻部洲</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>读书会17_菩萨道思 L90: [00:05:10.760] 佛陀说，我当时非常有智慧，到达这个国家以后，那里的老师看到我的杰出，让我当教授师的助理。当时，阎浮提洲，那边来</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>读书会17_菩萨道思 L156: [00:05:10.760] 佛陀说，我当时非常有智慧，到达这个国家以后，那里的老师看到我的杰出，让我当教授师的助理。当时，阎浮提洲，那边来</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>弥兰陀</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>弥林德</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>读书会19_戒定慧三 L264: &gt; [00:01:33.100] 大家可以去看那个《弥兰陀王问经》。弥林达，请问经？</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>读书会19_戒定慧三 L266: &gt; [00:01:39.375] 弥兰陀王就问过这个龙军尊者这样的问题。龙君尊者，</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>阿那律</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>阿奴卢特</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>读书会25_随念修习 L728: &gt; 提示：引出材料⑥录音 [00:14:21]–[00:20:09] 的因缘——**安吉罗天子**曾以**一万年**、**十二由旬**的布施</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>读书会25_随念修习 L453: &gt; 提示：引出材料⑥录音 [00:14:21]–[00:20:09] 的因缘——**安吉罗天子**曾以**一万年**、**十二由旬**的布施</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>波斯匿</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>巴谢那地</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>读书会13_业与轮回 L252: 5. **照录纪律**：共读原文一律照读，不擅自增删改。音声转写中的明显同音错字已校对（如"足道／主道"＝业道、"称入业／称怒"＝嗔怒、"不</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>读书会21_破妄显真 L309: - 校注：巴利语术语与明显同音错字已校正，其余口语原貌（含重复、口头语、未完成的句子）一律保留。主要校正：「迷人感／李染／李然／礼让／离然／</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>毗婆尸</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>维巴西</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>读书会11_十二缘起 L410: - 《因缘品 Nidānavaggapāḷi.pdf》——本讲材料③取"缘起经／分别经／毗婆尸经／无明缘经"段，"此有故彼有……此灭故彼灭"</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>弥兰陀王问经</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>《弥兰王问》</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>读书会19_戒定慧三 L264: &gt; [00:01:33.100] 大家可以去看那个《弥兰陀王问经》。弥林达，请问经？</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>蓝毗尼</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>伦比尼</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>读书会03_四护卫禅 L43: &gt; 今天是《四护卫禅实修》读书会的第四周。开始之前，请想像两千六百多年前的一个月圆之夜：在蓝毗尼园，一位王子降生了，落地走了七步；三十五年后</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>毗尼</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>律</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>读书会03_四护卫禅 L43: &gt; 今天是《四护卫禅实修》读书会的第四周。开始之前，请想像两千六百多年前的一个月圆之夜：在蓝毗尼园，一位王子降生了，落地走了七步；三十五年后</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>波罗提木叉</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>巴帝摩卡</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>读书会04_持戒与戒 L405: - **布萨（诵戒）**：僧团每半月集会诵波罗提木叉；“若有犯戒者应当发露，若无犯戒则应保持沉默”（材料③、扩展①）。</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>大迦叶</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>马哈咖沙巴</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>读书会09_四圣谛（ L47: &gt; 今天还会读到一批很美的经文——觉支相应。佛陀说，七觉支就像尖顶阁上的椽木，根根朝向顶尖；修习它们，心就"倾向涅槃、朝向涅槃、指向涅槃"。</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F71"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>